--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/FLORIDA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/FLORIDA_2024.xlsx
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C207">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C340">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Huichapa</t>
+          <t>Huichapan</t>
         </is>
       </c>
       <c r="C472">
